--- a/data/trans_orig/P1801_2016_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1801_2016_2023-Habitat-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>306770</t>
+          <t>306661</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>357952</t>
+          <t>359881</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>387362</t>
+          <t>388835</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>438621</t>
+          <t>439247</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>708707</t>
+          <t>707802</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>783243</t>
+          <t>777977</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>57,73%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>316848</t>
+          <t>314919</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>368030</t>
+          <t>368139</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>234218</t>
+          <t>233592</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>285477</t>
+          <t>284004</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>564396</t>
+          <t>569662</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>638932</t>
+          <t>639837</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>47,48%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>420436</t>
+          <t>422645</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>489741</t>
+          <t>486052</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>552717</t>
+          <t>555514</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>618771</t>
+          <t>620963</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>53,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>998532</t>
+          <t>990803</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1087567</t>
+          <t>1088136</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>52,69%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>532690</t>
+          <t>536379</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>601995</t>
+          <t>599786</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>58,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>424142</t>
+          <t>421950</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>490196</t>
+          <t>487399</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>977777</t>
+          <t>977208</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1066812</t>
+          <t>1074541</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>52,03%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>322447</t>
+          <t>324514</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>380510</t>
+          <t>380816</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>443817</t>
+          <t>441277</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>495447</t>
+          <t>499279</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>63,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>780031</t>
+          <t>780812</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>862634</t>
+          <t>864476</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>55,97%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>379042</t>
+          <t>378736</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>437105</t>
+          <t>435038</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>289564</t>
+          <t>285732</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>341194</t>
+          <t>343734</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>681929</t>
+          <t>680087</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>764532</t>
+          <t>763751</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>49,45%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>409130</t>
+          <t>408360</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>470740</t>
+          <t>468670</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>522601</t>
+          <t>522501</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>588181</t>
+          <t>591452</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>56,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>951690</t>
+          <t>950872</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1041629</t>
+          <t>1042577</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>52,62%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>466827</t>
+          <t>468897</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>528437</t>
+          <t>529207</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>455598</t>
+          <t>452327</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>521178</t>
+          <t>521278</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>939717</t>
+          <t>938769</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1029656</t>
+          <t>1030474</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>52,01%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1517483</t>
+          <t>1524395</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1638137</t>
+          <t>1638978</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1966592</t>
+          <t>1962823</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2083332</t>
+          <t>2088270</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3512610</t>
+          <t>3525518</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3685006</t>
+          <t>3700078</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>53,32%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1756213</t>
+          <t>1755372</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1876867</t>
+          <t>1869955</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1461210</t>
+          <t>1456272</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1577950</t>
+          <t>1581719</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3253886</t>
+          <t>3238814</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3426282</t>
+          <t>3413374</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>49,19%</t>
         </is>
       </c>
     </row>
@@ -2673,32 +2673,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>327805</t>
+          <t>349910</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>299411</t>
+          <t>321585</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>354588</t>
+          <t>379701</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2708,32 +2708,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>381614</t>
+          <t>410360</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>359436</t>
+          <t>389373</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>401150</t>
+          <t>432388</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>53,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2743,32 +2743,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>709419</t>
+          <t>760271</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>674532</t>
+          <t>724317</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>745203</t>
+          <t>796655</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>55,97%</t>
         </is>
       </c>
     </row>
@@ -2786,32 +2786,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>307636</t>
+          <t>340800</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>280853</t>
+          <t>311009</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>336030</t>
+          <t>369125</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2821,32 +2821,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>293622</t>
+          <t>322215</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>274086</t>
+          <t>300187</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>315800</t>
+          <t>343202</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2856,32 +2856,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>601258</t>
+          <t>663014</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>565474</t>
+          <t>626630</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>636145</t>
+          <t>698968</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>49,11%</t>
         </is>
       </c>
     </row>
@@ -2899,17 +2899,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2934,17 +2934,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675236</t>
+          <t>732575</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675236</t>
+          <t>732575</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675236</t>
+          <t>732575</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2969,17 +2969,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1310677</t>
+          <t>1423285</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1310677</t>
+          <t>1423285</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1310677</t>
+          <t>1423285</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>722059</t>
+          <t>509539</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>590268</t>
+          <t>475758</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>978648</t>
+          <t>545410</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>559657</t>
+          <t>622446</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>533946</t>
+          <t>590035</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>586857</t>
+          <t>650531</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1281716</t>
+          <t>1131985</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1155743</t>
+          <t>1083008</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1568152</t>
+          <t>1181201</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>51,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>55,77%</t>
         </is>
       </c>
     </row>
@@ -3129,32 +3129,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>469815</t>
+          <t>538308</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>213226</t>
+          <t>502437</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>601606</t>
+          <t>572089</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3164,32 +3164,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>397528</t>
+          <t>447503</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>370328</t>
+          <t>419418</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>423239</t>
+          <t>479914</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3199,32 +3199,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>867343</t>
+          <t>985811</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>580907</t>
+          <t>936595</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>993316</t>
+          <t>1034788</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>48,86%</t>
         </is>
       </c>
     </row>
@@ -3242,17 +3242,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1191874</t>
+          <t>1047847</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1191874</t>
+          <t>1047847</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1191874</t>
+          <t>1047847</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3277,17 +3277,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>957185</t>
+          <t>1069949</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>957185</t>
+          <t>1069949</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>957185</t>
+          <t>1069949</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3312,17 +3312,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2149059</t>
+          <t>2117796</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2149059</t>
+          <t>2117796</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2149059</t>
+          <t>2117796</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3359,32 +3359,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>286919</t>
+          <t>322515</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>257889</t>
+          <t>289157</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>317754</t>
+          <t>353157</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3394,32 +3394,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>537172</t>
+          <t>397119</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>413182</t>
+          <t>370018</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>728888</t>
+          <t>424710</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3429,32 +3429,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>824090</t>
+          <t>719634</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>686159</t>
+          <t>678406</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1118227</t>
+          <t>763789</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>47,4%</t>
         </is>
       </c>
     </row>
@@ -3472,32 +3472,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>416718</t>
+          <t>479431</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>385883</t>
+          <t>448789</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>445748</t>
+          <t>512789</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3507,32 +3507,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>394796</t>
+          <t>412169</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>203080</t>
+          <t>384578</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>518786</t>
+          <t>439270</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3542,32 +3542,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>811514</t>
+          <t>891600</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>517377</t>
+          <t>847445</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>949445</t>
+          <t>932828</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>57,9%</t>
         </is>
       </c>
     </row>
@@ -3585,17 +3585,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>703637</t>
+          <t>801946</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>703637</t>
+          <t>801946</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>703637</t>
+          <t>801946</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3620,17 +3620,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>931968</t>
+          <t>809288</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>931968</t>
+          <t>809288</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>931968</t>
+          <t>809288</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3655,17 +3655,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1635604</t>
+          <t>1611234</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1635604</t>
+          <t>1611234</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1635604</t>
+          <t>1611234</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3702,32 +3702,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>490040</t>
+          <t>509697</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>455470</t>
+          <t>475381</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>520509</t>
+          <t>542390</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3737,32 +3737,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>609811</t>
+          <t>654638</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>488112</t>
+          <t>621838</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>663505</t>
+          <t>683786</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>58,66%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3772,32 +3772,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1099851</t>
+          <t>1164335</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>963781</t>
+          <t>1116971</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1155222</t>
+          <t>1210190</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>57,49%</t>
         </is>
       </c>
     </row>
@@ -3815,32 +3815,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>435509</t>
+          <t>479287</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>405040</t>
+          <t>446594</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>470079</t>
+          <t>513603</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3850,32 +3850,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>482106</t>
+          <t>461317</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>428412</t>
+          <t>432169</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>603805</t>
+          <t>494117</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3885,32 +3885,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>917615</t>
+          <t>940604</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>862244</t>
+          <t>894749</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1053685</t>
+          <t>987968</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>46,94%</t>
         </is>
       </c>
     </row>
@@ -3928,17 +3928,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>925549</t>
+          <t>988984</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>925549</t>
+          <t>988984</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>925549</t>
+          <t>988984</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -3963,17 +3963,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1091917</t>
+          <t>1115955</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1091917</t>
+          <t>1115955</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1091917</t>
+          <t>1115955</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3998,17 +3998,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2017466</t>
+          <t>2104939</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2017466</t>
+          <t>2104939</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2017466</t>
+          <t>2104939</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4045,32 +4045,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1826823</t>
+          <t>1691660</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1682575</t>
+          <t>1626326</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2227435</t>
+          <t>1757140</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4080,32 +4080,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2088253</t>
+          <t>2084564</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1952295</t>
+          <t>2026244</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2367460</t>
+          <t>2136118</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4115,32 +4115,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>3915075</t>
+          <t>3776224</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3688333</t>
+          <t>3695188</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4351924</t>
+          <t>3868475</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>50,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>53,3%</t>
         </is>
       </c>
     </row>
@@ -4158,32 +4158,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1629678</t>
+          <t>1837826</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1229066</t>
+          <t>1772346</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1773926</t>
+          <t>1903160</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4193,32 +4193,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1568052</t>
+          <t>1643204</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1288845</t>
+          <t>1591650</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1704010</t>
+          <t>1701524</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4228,32 +4228,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>3197731</t>
+          <t>3481030</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2760882</t>
+          <t>3388779</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3424473</t>
+          <t>3562066</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>49,08%</t>
         </is>
       </c>
     </row>
@@ -4271,17 +4271,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3456501</t>
+          <t>3529486</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3456501</t>
+          <t>3529486</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3456501</t>
+          <t>3529486</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4306,17 +4306,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3656305</t>
+          <t>3727768</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3656305</t>
+          <t>3727768</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3656305</t>
+          <t>3727768</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4341,17 +4341,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7112806</t>
+          <t>7257254</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7112806</t>
+          <t>7257254</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7112806</t>
+          <t>7257254</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
